--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/2_four_bus_radial_2ph_grid_MP_pf_sc_results_0_bus.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/2_four_bus_radial_2ph_grid_MP_pf_sc_results_0_bus.xlsx
@@ -68,9 +68,6 @@
     <t>pf_va_degree</t>
   </si>
   <si>
-    <t>Bus_0</t>
-  </si>
-  <si>
     <t>Bus_1</t>
   </si>
   <si>
@@ -78,6 +75,9 @@
   </si>
   <si>
     <t>Bus_3</t>
+  </si>
+  <si>
+    <t>Bus_0</t>
   </si>
   <si>
     <t>pf_ikss_a_ka</t>
@@ -523,22 +523,22 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>144.3375636545937</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>99.99999896630133</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>0.0001671662503139904</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0.001671662470412813</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>84.28940675143633</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -592,22 +592,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>144.3375636545937</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>99.99999896630133</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>0.0001671662503139904</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>0.001671662470412813</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>84.28940675143633</v>
       </c>
     </row>
   </sheetData>
@@ -681,7 +681,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -740,7 +740,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -799,7 +799,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -858,7 +858,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1045,7 +1045,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1104,7 +1104,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1163,7 +1163,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1291,7 +1291,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1350,7 +1350,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1409,7 +1409,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1468,7 +1468,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1596,7 +1596,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1655,7 +1655,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1714,7 +1714,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1901,7 +1901,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1960,7 +1960,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2019,7 +2019,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2078,7 +2078,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2206,7 +2206,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2265,7 +2265,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2324,7 +2324,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2383,7 +2383,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2511,7 +2511,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2570,7 +2570,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2629,7 +2629,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2819,7 +2819,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>144.3373610443744</v>
@@ -2881,7 +2881,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2943,7 +2943,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3005,7 +3005,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3139,7 +3139,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>144.3373610798029</v>
@@ -3201,7 +3201,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3263,7 +3263,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3325,7 +3325,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3459,7 +3459,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0.03428655024571495</v>
@@ -3521,7 +3521,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3583,7 +3583,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3645,7 +3645,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3740,7 +3740,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>144.3375733382017</v>
@@ -3763,7 +3763,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3786,7 +3786,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3809,7 +3809,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3904,7 +3904,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0.03591893102360295</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4090,7 +4090,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>115.469871493791</v>
@@ -4286,7 +4286,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4348,7 +4348,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4410,7 +4410,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4544,7 +4544,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>115.4698795269446</v>
@@ -4606,7 +4606,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4668,7 +4668,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4730,7 +4730,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4864,7 +4864,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0.03102041859591505</v>
@@ -4926,7 +4926,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4988,7 +4988,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -5050,7 +5050,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -5184,7 +5184,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0.02938808621826369</v>
@@ -5246,7 +5246,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5308,7 +5308,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -5504,7 +5504,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -5566,7 +5566,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5628,7 +5628,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -5690,7 +5690,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -5824,7 +5824,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -5886,7 +5886,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5948,7 +5948,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -6010,7 +6010,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -6144,7 +6144,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -6206,7 +6206,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6268,7 +6268,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -6330,7 +6330,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -6464,7 +6464,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -6526,7 +6526,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6588,7 +6588,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -6650,7 +6650,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -6784,7 +6784,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -6846,7 +6846,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6908,7 +6908,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -6970,7 +6970,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -7065,7 +7065,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0.0342865502553216</v>
@@ -7088,7 +7088,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -7111,7 +7111,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -7134,7 +7134,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -7229,7 +7229,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -7291,7 +7291,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -7353,7 +7353,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -7415,7 +7415,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -7549,7 +7549,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -7611,7 +7611,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -7673,7 +7673,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -7735,7 +7735,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -7869,7 +7869,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -7931,7 +7931,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -7993,7 +7993,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8055,7 +8055,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -8150,7 +8150,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0.03591893103464823</v>
@@ -8173,7 +8173,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -8196,7 +8196,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8219,7 +8219,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -8275,7 +8275,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>115.4700547192921</v>
@@ -8298,7 +8298,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -8321,7 +8321,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8344,7 +8344,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -8400,7 +8400,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>115.4700531090195</v>
@@ -8423,7 +8423,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -8446,7 +8446,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8469,7 +8469,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -8525,7 +8525,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0.03102041860706187</v>
@@ -8548,7 +8548,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -8571,7 +8571,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8594,7 +8594,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -8650,7 +8650,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0.02938808622774167</v>
@@ -8673,7 +8673,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -8696,7 +8696,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8719,7 +8719,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -8811,7 +8811,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -8870,7 +8870,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -8929,7 +8929,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8988,7 +8988,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>0</v>
